--- a/artfynd/A 20307-2025 artfynd.xlsx
+++ b/artfynd/A 20307-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137311694</v>
       </c>
       <c r="B2" t="n">
-        <v>91934</v>
+        <v>91935</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137307708</v>
       </c>
       <c r="B3" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137307721</v>
       </c>
       <c r="B4" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137311689</v>
       </c>
       <c r="B5" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137311695</v>
       </c>
       <c r="B6" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137311699</v>
       </c>
       <c r="B7" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137311700</v>
       </c>
       <c r="B8" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137311705</v>
       </c>
       <c r="B9" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137311707</v>
       </c>
       <c r="B10" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137311759</v>
       </c>
       <c r="B11" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137311772</v>
       </c>
       <c r="B12" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137311774</v>
       </c>
       <c r="B13" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137311777</v>
       </c>
       <c r="B14" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137307711</v>
       </c>
       <c r="B15" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137311698</v>
       </c>
       <c r="B16" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137311764</v>
       </c>
       <c r="B17" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137307719</v>
       </c>
       <c r="B18" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137307720</v>
       </c>
       <c r="B19" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137311693</v>
       </c>
       <c r="B20" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137307718</v>
       </c>
       <c r="B21" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137307717</v>
       </c>
       <c r="B22" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137311767</v>
       </c>
       <c r="B23" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137311742</v>
       </c>
       <c r="B24" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>137311761</v>
       </c>
       <c r="B25" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>137311765</v>
       </c>
       <c r="B26" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>137311769</v>
       </c>
       <c r="B27" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>137307712</v>
       </c>
       <c r="B28" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>137307715</v>
       </c>
       <c r="B29" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>137311763</v>
       </c>
       <c r="B30" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>137311771</v>
       </c>
       <c r="B31" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>137311766</v>
       </c>
       <c r="B32" t="n">
-        <v>87546</v>
+        <v>87547</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>137307707</v>
       </c>
       <c r="B33" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>137307710</v>
       </c>
       <c r="B34" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>137307713</v>
       </c>
       <c r="B35" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>137307716</v>
       </c>
       <c r="B36" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>137311690</v>
       </c>
       <c r="B37" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>137311692</v>
       </c>
       <c r="B38" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>137311697</v>
       </c>
       <c r="B39" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>137311708</v>
       </c>
       <c r="B40" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>137311760</v>
       </c>
       <c r="B41" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>137311773</v>
       </c>
       <c r="B42" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 20307-2025 artfynd.xlsx
+++ b/artfynd/A 20307-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137311694</v>
       </c>
       <c r="B2" t="n">
-        <v>91935</v>
+        <v>91938</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137307708</v>
       </c>
       <c r="B3" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137307721</v>
       </c>
       <c r="B4" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137311689</v>
       </c>
       <c r="B5" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137311695</v>
       </c>
       <c r="B6" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137311699</v>
       </c>
       <c r="B7" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137311700</v>
       </c>
       <c r="B8" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137311705</v>
       </c>
       <c r="B9" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137311707</v>
       </c>
       <c r="B10" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137311759</v>
       </c>
       <c r="B11" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137311772</v>
       </c>
       <c r="B12" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137311774</v>
       </c>
       <c r="B13" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137311777</v>
       </c>
       <c r="B14" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137307711</v>
       </c>
       <c r="B15" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137311698</v>
       </c>
       <c r="B16" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137311764</v>
       </c>
       <c r="B17" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137307719</v>
       </c>
       <c r="B18" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137307720</v>
       </c>
       <c r="B19" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137311693</v>
       </c>
       <c r="B20" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137307718</v>
       </c>
       <c r="B21" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137307717</v>
       </c>
       <c r="B22" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137311767</v>
       </c>
       <c r="B23" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137311742</v>
       </c>
       <c r="B24" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>137311761</v>
       </c>
       <c r="B25" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>137311765</v>
       </c>
       <c r="B26" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>137311769</v>
       </c>
       <c r="B27" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>137307712</v>
       </c>
       <c r="B28" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>137307715</v>
       </c>
       <c r="B29" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>137311763</v>
       </c>
       <c r="B30" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>137311771</v>
       </c>
       <c r="B31" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>137311766</v>
       </c>
       <c r="B32" t="n">
-        <v>87547</v>
+        <v>87550</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>137307707</v>
       </c>
       <c r="B33" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>137307710</v>
       </c>
       <c r="B34" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>137307713</v>
       </c>
       <c r="B35" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>137307716</v>
       </c>
       <c r="B36" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>137311690</v>
       </c>
       <c r="B37" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>137311692</v>
       </c>
       <c r="B38" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>137311697</v>
       </c>
       <c r="B39" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>137311708</v>
       </c>
       <c r="B40" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>137311760</v>
       </c>
       <c r="B41" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>137311773</v>
       </c>
       <c r="B42" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 20307-2025 artfynd.xlsx
+++ b/artfynd/A 20307-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ42"/>
+  <dimension ref="A1:AZ59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137311694</v>
       </c>
       <c r="B2" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2136,48 +2136,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137307711</v>
+        <v>137387594</v>
       </c>
       <c r="B15" t="n">
-        <v>87397</v>
+        <v>87536</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mästerby Salmunds, Gtl</t>
+          <t>Mästerby, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696150</v>
+        <v>696181</v>
       </c>
       <c r="R15" t="n">
-        <v>6376420</v>
+        <v>6376468</v>
       </c>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,49 +2231,49 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137307711</t>
+          <t>https://artportalen.se/Sighting/137387594</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137311698</v>
+        <v>137387603</v>
       </c>
       <c r="B16" t="n">
-        <v>87397</v>
+        <v>87536</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,13 +2283,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696191</v>
+        <v>696164</v>
       </c>
       <c r="R16" t="n">
-        <v>6376335</v>
+        <v>6376352</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,49 +2343,49 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137311698</t>
+          <t>https://artportalen.se/Sighting/137387603</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137311764</v>
+        <v>137387605</v>
       </c>
       <c r="B17" t="n">
-        <v>87397</v>
+        <v>87536</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,13 +2395,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696205</v>
+        <v>696125</v>
       </c>
       <c r="R17" t="n">
-        <v>6376350</v>
+        <v>6376363</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2455,27 +2455,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Nicolai Berg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Nicolai Berg, Oskar Karl Elias Olsson, Rasid Klimenta, Emma Nordenberg, Cecilia Carlén, Meandra Sewell</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137311764</t>
+          <t>https://artportalen.se/Sighting/137387605</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137307719</v>
+        <v>137387607</v>
       </c>
       <c r="B18" t="n">
-        <v>87373</v>
+        <v>87536</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2483,37 +2483,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mästerby Salmunds, Gtl</t>
+          <t>Mästerby, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696112</v>
+        <v>696132</v>
       </c>
       <c r="R18" t="n">
-        <v>6376285</v>
+        <v>6376423</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2567,27 +2567,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137307719</t>
+          <t>https://artportalen.se/Sighting/137387607</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137307720</v>
+        <v>137387612</v>
       </c>
       <c r="B19" t="n">
-        <v>87373</v>
+        <v>87536</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,37 +2595,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mästerby Salmunds, Gtl</t>
+          <t>Mästerby, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696113</v>
+        <v>696183</v>
       </c>
       <c r="R19" t="n">
-        <v>6376278</v>
+        <v>6376442</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2679,65 +2679,65 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137307720</t>
+          <t>https://artportalen.se/Sighting/137387612</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137311693</v>
+        <v>137307711</v>
       </c>
       <c r="B20" t="n">
-        <v>87373</v>
+        <v>87397</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mästerby, Gtl</t>
+          <t>Mästerby Salmunds, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696204</v>
+        <v>696150</v>
       </c>
       <c r="R20" t="n">
-        <v>6376390</v>
+        <v>6376420</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2791,27 +2791,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137311693</t>
+          <t>https://artportalen.se/Sighting/137307711</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137307718</v>
+        <v>137311698</v>
       </c>
       <c r="B21" t="n">
-        <v>93473</v>
+        <v>87397</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2819,37 +2819,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4366</v>
+        <v>3712</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mästerby Salmunds, Gtl</t>
+          <t>Mästerby, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696129</v>
+        <v>696191</v>
       </c>
       <c r="R21" t="n">
-        <v>6376295</v>
+        <v>6376335</v>
       </c>
       <c r="S21" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2903,65 +2903,65 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137307718</t>
+          <t>https://artportalen.se/Sighting/137311698</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137307717</v>
+        <v>137311764</v>
       </c>
       <c r="B22" t="n">
-        <v>93132</v>
+        <v>87397</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4769</v>
+        <v>3712</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mästerby Salmunds, Gtl</t>
+          <t>Mästerby, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696152</v>
+        <v>696205</v>
       </c>
       <c r="R22" t="n">
-        <v>6376325</v>
+        <v>6376350</v>
       </c>
       <c r="S22" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3015,27 +3015,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Nicolai Berg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Rasid Klimenta, Emma Nordenberg, Cecilia Carlén, Meandra Sewell</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137307717</t>
+          <t>https://artportalen.se/Sighting/137311764</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137311767</v>
+        <v>137387598</v>
       </c>
       <c r="B23" t="n">
-        <v>93497</v>
+        <v>87397</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3043,21 +3043,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5964</v>
+        <v>3712</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696293</v>
+        <v>696196</v>
       </c>
       <c r="R23" t="n">
-        <v>6376139</v>
+        <v>6376362</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3127,76 +3127,65 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Nicolai Berg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Nicolai Berg, Oskar Karl Elias Olsson, Rasid Klimenta, Emma Nordenberg, Cecilia Carlén, Meandra Sewell</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137311767</t>
+          <t>https://artportalen.se/Sighting/137387598</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137311742</v>
+        <v>137387602</v>
       </c>
       <c r="B24" t="n">
-        <v>87596</v>
+        <v>87397</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>248947</v>
+        <v>3712</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mästerby , Gtl</t>
+          <t>Mästerby, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696203</v>
+        <v>696170</v>
       </c>
       <c r="R24" t="n">
-        <v>6376343</v>
+        <v>6376351</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3223,14 +3212,19 @@
           <t>2026-10-17</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>En spindling från sect. Calochroi, som vid KOH-droppande blev rosaröd på fotknölen. :)</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3239,56 +3233,55 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Oskar Karl Elias Olsson</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Oskar Karl Elias Olsson, Nicolai Berg, Emma Nordenberg, Cecilia Carlén , Rasid Klimenta, Meandra Sewell</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137311742</t>
+          <t>https://artportalen.se/Sighting/137387602</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>137311761</v>
+        <v>137387606</v>
       </c>
       <c r="B25" t="n">
-        <v>87596</v>
+        <v>87397</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>248947</v>
+        <v>3712</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3298,13 +3291,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696220</v>
+        <v>696124</v>
       </c>
       <c r="R25" t="n">
-        <v>6376404</v>
+        <v>6376366</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3333,7 +3326,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3343,7 +3336,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3358,49 +3351,49 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Nicolai Berg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Nicolai Berg, Oskar Karl Elias Olsson, Rasid Klimenta, Emma Nordenberg, Cecilia Carlén, Meandra Sewell</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137311761</t>
+          <t>https://artportalen.se/Sighting/137387606</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137311765</v>
+        <v>137387610</v>
       </c>
       <c r="B26" t="n">
-        <v>87596</v>
+        <v>87397</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>248947</v>
+        <v>3712</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3410,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696208</v>
+        <v>696145</v>
       </c>
       <c r="R26" t="n">
-        <v>6376310</v>
+        <v>6376427</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3445,7 +3438,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3455,7 +3448,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3464,72 +3457,71 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Nicolai Berg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Nicolai Berg, Oskar Karl Elias Olsson, Rasid Klimenta, Emma Nordenberg, Cecilia Carlén, Meandra Sewell</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137311765</t>
+          <t>https://artportalen.se/Sighting/137387610</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137311769</v>
+        <v>137307719</v>
       </c>
       <c r="B27" t="n">
-        <v>87596</v>
+        <v>87373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>248947</v>
+        <v>3762</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mästerby, Gtl</t>
+          <t>Mästerby Salmunds, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696313</v>
+        <v>696112</v>
       </c>
       <c r="R27" t="n">
-        <v>6376136</v>
+        <v>6376285</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3558,7 +3550,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3568,7 +3560,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3583,49 +3575,49 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Nicolai Berg</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Nicolai Berg, Oskar Karl Elias Olsson, Rasid Klimenta, Emma Nordenberg, Cecilia Carlén, Meandra Sewell</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137311769</t>
+          <t>https://artportalen.se/Sighting/137307719</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137307712</v>
+        <v>137307720</v>
       </c>
       <c r="B28" t="n">
-        <v>87489</v>
+        <v>87373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>248956</v>
+        <v>3762</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3635,13 +3627,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696150</v>
+        <v>696113</v>
       </c>
       <c r="R28" t="n">
-        <v>6376420</v>
+        <v>6376278</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3670,7 +3662,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3680,7 +3672,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3706,51 +3698,51 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137307712</t>
+          <t>https://artportalen.se/Sighting/137307720</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137307715</v>
+        <v>137311693</v>
       </c>
       <c r="B29" t="n">
-        <v>87489</v>
+        <v>87373</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>248956</v>
+        <v>3762</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mästerby Salmunds, Gtl</t>
+          <t>Mästerby, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696151</v>
+        <v>696204</v>
       </c>
       <c r="R29" t="n">
-        <v>6376435</v>
+        <v>6376390</v>
       </c>
       <c r="S29" t="n">
         <v>6</v>
@@ -3782,7 +3774,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3792,7 +3784,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3807,49 +3799,49 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137307715</t>
+          <t>https://artportalen.se/Sighting/137311693</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137311763</v>
+        <v>137387597</v>
       </c>
       <c r="B30" t="n">
-        <v>87489</v>
+        <v>87373</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>248956</v>
+        <v>3762</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3859,13 +3851,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696204</v>
+        <v>696196</v>
       </c>
       <c r="R30" t="n">
-        <v>6376350</v>
+        <v>6376373</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3894,7 +3886,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3904,7 +3896,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3919,49 +3911,49 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Nicolai Berg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Nicolai Berg, Oskar Karl Elias Olsson, Rasid Klimenta, Emma Nordenberg, Cecilia Carlén, Meandra Sewell</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137311763</t>
+          <t>https://artportalen.se/Sighting/137387597</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137311771</v>
+        <v>137387611</v>
       </c>
       <c r="B31" t="n">
-        <v>87489</v>
+        <v>87373</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>248956</v>
+        <v>3762</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3971,13 +3963,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696314</v>
+        <v>696173</v>
       </c>
       <c r="R31" t="n">
-        <v>6376143</v>
+        <v>6376443</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4006,7 +3998,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4016,7 +4008,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4031,27 +4023,27 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Nicolai Berg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Nicolai Berg, Oskar Karl Elias Olsson, Rasid Klimenta, Emma Nordenberg, Cecilia Carlén, Meandra Sewell</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137311771</t>
+          <t>https://artportalen.se/Sighting/137387611</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137311766</v>
+        <v>137307718</v>
       </c>
       <c r="B32" t="n">
-        <v>87550</v>
+        <v>93475</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4059,37 +4051,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>249228</v>
+        <v>4366</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mästerby, Gtl</t>
+          <t>Mästerby Salmunds, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696266</v>
+        <v>696129</v>
       </c>
       <c r="R32" t="n">
-        <v>6376153</v>
+        <v>6376295</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4118,7 +4110,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4128,7 +4120,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4137,56 +4129,55 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Nicolai Berg</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Nicolai Berg, Oskar Karl Elias Olsson, Rasid Klimenta, Emma Nordenberg, Cecilia Carlén, Meandra Sewell</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137311766</t>
+          <t>https://artportalen.se/Sighting/137307718</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137307707</v>
+        <v>137307717</v>
       </c>
       <c r="B33" t="n">
-        <v>87573</v>
+        <v>93134</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6003295</v>
+        <v>4769</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4196,13 +4187,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696180</v>
+        <v>696152</v>
       </c>
       <c r="R33" t="n">
-        <v>6376470</v>
+        <v>6376325</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4231,7 +4222,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4241,7 +4232,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4250,7 +4241,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4268,16 +4258,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137307707</t>
+          <t>https://artportalen.se/Sighting/137307717</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>137307710</v>
+        <v>137311767</v>
       </c>
       <c r="B34" t="n">
-        <v>87573</v>
+        <v>93499</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,37 +4275,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mästerby Salmunds, Gtl</t>
+          <t>Mästerby, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696136</v>
+        <v>696293</v>
       </c>
       <c r="R34" t="n">
-        <v>6376469</v>
+        <v>6376139</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4344,7 +4334,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4354,7 +4344,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4363,34 +4353,33 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Nicolai Berg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Rasid Klimenta, Emma Nordenberg, Cecilia Carlén, Meandra Sewell</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137307710</t>
+          <t>https://artportalen.se/Sighting/137311767</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>137307713</v>
+        <v>137387600</v>
       </c>
       <c r="B35" t="n">
-        <v>87573</v>
+        <v>93499</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4398,34 +4387,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mästerby Salmunds, Gtl</t>
+          <t>Mästerby, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696148</v>
+        <v>696182</v>
       </c>
       <c r="R35" t="n">
-        <v>6376422</v>
+        <v>6376335</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4457,7 +4446,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4467,7 +4456,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4476,34 +4465,33 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137307713</t>
+          <t>https://artportalen.se/Sighting/137387600</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>137307716</v>
+        <v>137387604</v>
       </c>
       <c r="B36" t="n">
-        <v>87573</v>
+        <v>93499</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4511,37 +4499,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mästerby Salmunds, Gtl</t>
+          <t>Mästerby, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>696172</v>
+        <v>696125</v>
       </c>
       <c r="R36" t="n">
-        <v>6376387</v>
+        <v>6376363</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4570,7 +4558,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4580,7 +4568,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4589,72 +4577,82 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137307716</t>
+          <t>https://artportalen.se/Sighting/137387604</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>137311690</v>
+        <v>137311742</v>
       </c>
       <c r="B37" t="n">
-        <v>87573</v>
+        <v>87596</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6003295</v>
+        <v>248947</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mästerby, Gtl</t>
+          <t>Mästerby , Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>696195</v>
+        <v>696203</v>
       </c>
       <c r="R37" t="n">
-        <v>6376431</v>
+        <v>6376343</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4681,19 +4679,14 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>14:49</t>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>En spindling från sect. Calochroi, som vid KOH-droppande blev rosaröd på fotknölen. :)</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4709,49 +4702,49 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Oskar Karl Elias Olsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Oskar Karl Elias Olsson, Nicolai Berg, Emma Nordenberg, Cecilia Carlén , Rasid Klimenta, Meandra Sewell</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137311690</t>
+          <t>https://artportalen.se/Sighting/137311742</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>137311692</v>
+        <v>137311761</v>
       </c>
       <c r="B38" t="n">
-        <v>87573</v>
+        <v>87596</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6003295</v>
+        <v>248947</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4761,13 +4754,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>696215</v>
+        <v>696220</v>
       </c>
       <c r="R38" t="n">
-        <v>6376394</v>
+        <v>6376404</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4796,7 +4789,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4806,7 +4799,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4815,56 +4808,55 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Nicolai Berg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Rasid Klimenta, Emma Nordenberg, Cecilia Carlén, Meandra Sewell</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137311692</t>
+          <t>https://artportalen.se/Sighting/137311761</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>137311697</v>
+        <v>137311765</v>
       </c>
       <c r="B39" t="n">
-        <v>87573</v>
+        <v>87596</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6003295</v>
+        <v>248947</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4874,13 +4866,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>696197</v>
+        <v>696208</v>
       </c>
       <c r="R39" t="n">
-        <v>6376375</v>
+        <v>6376310</v>
       </c>
       <c r="S39" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4909,7 +4901,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4919,7 +4911,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4935,49 +4927,49 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Nicolai Berg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Rasid Klimenta, Emma Nordenberg, Cecilia Carlén, Meandra Sewell</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137311697</t>
+          <t>https://artportalen.se/Sighting/137311765</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>137311708</v>
+        <v>137311769</v>
       </c>
       <c r="B40" t="n">
-        <v>87573</v>
+        <v>87596</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6003295</v>
+        <v>248947</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4987,13 +4979,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696181</v>
+        <v>696313</v>
       </c>
       <c r="R40" t="n">
-        <v>6376439</v>
+        <v>6376136</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5022,7 +5014,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5032,7 +5024,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5041,72 +5033,71 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Nicolai Berg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Rasid Klimenta, Emma Nordenberg, Cecilia Carlén, Meandra Sewell</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137311708</t>
+          <t>https://artportalen.se/Sighting/137311769</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>137311760</v>
+        <v>137307712</v>
       </c>
       <c r="B41" t="n">
-        <v>87573</v>
+        <v>87489</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mästerby, Gtl</t>
+          <t>Mästerby Salmunds, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696193</v>
+        <v>696150</v>
       </c>
       <c r="R41" t="n">
-        <v>6376433</v>
+        <v>6376420</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5135,7 +5126,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5145,7 +5136,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5154,75 +5145,71 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Nicolai Berg</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Nicolai Berg, Oskar Karl Elias Olsson, Rasid Klimenta, Emma Nordenberg, Cecilia Carlén, Meandra Sewell</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137311760</t>
+          <t>https://artportalen.se/Sighting/137307712</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>137311773</v>
+        <v>137307715</v>
       </c>
       <c r="B42" t="n">
-        <v>87573</v>
+        <v>87489</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mästerby, Gtl</t>
+          <t>Mästerby Salmunds, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>696420</v>
+        <v>696151</v>
       </c>
       <c r="R42" t="n">
-        <v>6376150</v>
+        <v>6376435</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5251,7 +5238,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5261,7 +5248,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5270,25 +5257,1944 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Nicolai Berg</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Nicolai Berg, Oskar Karl Elias Olsson, Rasid Klimenta, Emma Nordenberg, Cecilia Carlén, Meandra Sewell</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137307715</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>137311763</v>
+      </c>
+      <c r="B43" t="n">
+        <v>87489</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Mästerby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>696204</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6376350</v>
+      </c>
+      <c r="S43" t="n">
+        <v>7</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Mästerby</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Nicolai Berg</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Rasid Klimenta, Emma Nordenberg, Cecilia Carlén, Meandra Sewell</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137311763</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>137311771</v>
+      </c>
+      <c r="B44" t="n">
+        <v>87489</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Mästerby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>696314</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6376143</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Mästerby</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Nicolai Berg</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Rasid Klimenta, Emma Nordenberg, Cecilia Carlén, Meandra Sewell</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137311771</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>137387593</v>
+      </c>
+      <c r="B45" t="n">
+        <v>87489</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Mästerby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>696239</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6376483</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Mästerby</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137387593</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>137387595</v>
+      </c>
+      <c r="B46" t="n">
+        <v>87489</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Mästerby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>696199</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6376379</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Mästerby</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137387595</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>137311766</v>
+      </c>
+      <c r="B47" t="n">
+        <v>87550</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>249228</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Barrfagerspindling</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Mästerby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>696266</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6376153</v>
+      </c>
+      <c r="S47" t="n">
+        <v>9</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Mästerby</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Nicolai Berg</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Rasid Klimenta, Emma Nordenberg, Cecilia Carlén, Meandra Sewell</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137311766</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>137307707</v>
+      </c>
+      <c r="B48" t="n">
+        <v>87573</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Mästerby Salmunds, Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>696180</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6376470</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Mästerby</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137307707</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>137307710</v>
+      </c>
+      <c r="B49" t="n">
+        <v>87573</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Mästerby Salmunds, Gtl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>696136</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6376469</v>
+      </c>
+      <c r="S49" t="n">
+        <v>11</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Mästerby</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137307710</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>137307713</v>
+      </c>
+      <c r="B50" t="n">
+        <v>87573</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Mästerby Salmunds, Gtl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>696148</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6376422</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Mästerby</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137307713</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>137307716</v>
+      </c>
+      <c r="B51" t="n">
+        <v>87573</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Mästerby Salmunds, Gtl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>696172</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6376387</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Mästerby</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137307716</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>137311690</v>
+      </c>
+      <c r="B52" t="n">
+        <v>87573</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Mästerby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>696195</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6376431</v>
+      </c>
+      <c r="S52" t="n">
+        <v>7</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Mästerby</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137311690</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>137311692</v>
+      </c>
+      <c r="B53" t="n">
+        <v>87573</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Mästerby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>696215</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6376394</v>
+      </c>
+      <c r="S53" t="n">
+        <v>8</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Mästerby</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137311692</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>137311697</v>
+      </c>
+      <c r="B54" t="n">
+        <v>87573</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Mästerby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>696197</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6376375</v>
+      </c>
+      <c r="S54" t="n">
+        <v>12</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Mästerby</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137311697</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>137311708</v>
+      </c>
+      <c r="B55" t="n">
+        <v>87573</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Mästerby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>696181</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6376439</v>
+      </c>
+      <c r="S55" t="n">
+        <v>7</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Mästerby</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137311708</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>137311760</v>
+      </c>
+      <c r="B56" t="n">
+        <v>87573</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Mästerby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>696193</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6376433</v>
+      </c>
+      <c r="S56" t="n">
+        <v>6</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Mästerby</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Nicolai Berg</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Rasid Klimenta, Emma Nordenberg, Cecilia Carlén, Meandra Sewell</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137311760</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>137311773</v>
+      </c>
+      <c r="B57" t="n">
+        <v>87573</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Mästerby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>696420</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6376150</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Mästerby</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Nicolai Berg</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Rasid Klimenta, Emma Nordenberg, Cecilia Carlén, Meandra Sewell</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137311773</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>137387601</v>
+      </c>
+      <c r="B58" t="n">
+        <v>87573</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Mästerby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>696181</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6376336</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Mästerby</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137387601</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>137387609</v>
+      </c>
+      <c r="B59" t="n">
+        <v>87573</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Mästerby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>696130</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6376418</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Mästerby</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137387609</t>
         </is>
       </c>
     </row>
@@ -5335,6 +7241,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20307-2025 artfynd.xlsx
+++ b/artfynd/A 20307-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137311694</v>
       </c>
       <c r="B2" t="n">
-        <v>91940</v>
+        <v>91945</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137307708</v>
       </c>
       <c r="B3" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137307721</v>
       </c>
       <c r="B4" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137311689</v>
       </c>
       <c r="B5" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137311695</v>
       </c>
       <c r="B6" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137311699</v>
       </c>
       <c r="B7" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137311700</v>
       </c>
       <c r="B8" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137311705</v>
       </c>
       <c r="B9" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137311707</v>
       </c>
       <c r="B10" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137311759</v>
       </c>
       <c r="B11" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137311772</v>
       </c>
       <c r="B12" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137311774</v>
       </c>
       <c r="B13" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137311777</v>
       </c>
       <c r="B14" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137387594</v>
       </c>
       <c r="B15" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137387603</v>
       </c>
       <c r="B16" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137387605</v>
       </c>
       <c r="B17" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137387607</v>
       </c>
       <c r="B18" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137387612</v>
       </c>
       <c r="B19" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137307711</v>
       </c>
       <c r="B20" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137311698</v>
       </c>
       <c r="B21" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137311764</v>
       </c>
       <c r="B22" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137387598</v>
       </c>
       <c r="B23" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137387602</v>
       </c>
       <c r="B24" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137387606</v>
       </c>
       <c r="B25" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137387610</v>
       </c>
       <c r="B26" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137307719</v>
       </c>
       <c r="B27" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137307720</v>
       </c>
       <c r="B28" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>137311693</v>
       </c>
       <c r="B29" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>137387597</v>
       </c>
       <c r="B30" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137387611</v>
       </c>
       <c r="B31" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>137307718</v>
       </c>
       <c r="B32" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>137307717</v>
       </c>
       <c r="B33" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>137311767</v>
       </c>
       <c r="B34" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>137387600</v>
       </c>
       <c r="B35" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>137387604</v>
       </c>
       <c r="B36" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>137311742</v>
       </c>
       <c r="B37" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>137311761</v>
       </c>
       <c r="B38" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>137311765</v>
       </c>
       <c r="B39" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>137311769</v>
       </c>
       <c r="B40" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>137307712</v>
       </c>
       <c r="B41" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>137307715</v>
       </c>
       <c r="B42" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>137311763</v>
       </c>
       <c r="B43" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>137311771</v>
       </c>
       <c r="B44" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>137387593</v>
       </c>
       <c r="B45" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>137387595</v>
       </c>
       <c r="B46" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>137311766</v>
       </c>
       <c r="B47" t="n">
-        <v>87550</v>
+        <v>87555</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>137307707</v>
       </c>
       <c r="B48" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>137307710</v>
       </c>
       <c r="B49" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>137307713</v>
       </c>
       <c r="B50" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>137307716</v>
       </c>
       <c r="B51" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>137311690</v>
       </c>
       <c r="B52" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>137311692</v>
       </c>
       <c r="B53" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         <v>137311697</v>
       </c>
       <c r="B54" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>137311708</v>
       </c>
       <c r="B55" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>137311760</v>
       </c>
       <c r="B56" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>137311773</v>
       </c>
       <c r="B57" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>137387601</v>
       </c>
       <c r="B58" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>137387609</v>
       </c>
       <c r="B59" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 20307-2025 artfynd.xlsx
+++ b/artfynd/A 20307-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137311694</v>
       </c>
       <c r="B2" t="n">
-        <v>91945</v>
+        <v>91957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137307708</v>
       </c>
       <c r="B3" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137307721</v>
       </c>
       <c r="B4" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137311689</v>
       </c>
       <c r="B5" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137311695</v>
       </c>
       <c r="B6" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137311699</v>
       </c>
       <c r="B7" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137311700</v>
       </c>
       <c r="B8" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137311705</v>
       </c>
       <c r="B9" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137311707</v>
       </c>
       <c r="B10" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137311759</v>
       </c>
       <c r="B11" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137311772</v>
       </c>
       <c r="B12" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137311774</v>
       </c>
       <c r="B13" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137311777</v>
       </c>
       <c r="B14" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137387594</v>
       </c>
       <c r="B15" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137387603</v>
       </c>
       <c r="B16" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137387605</v>
       </c>
       <c r="B17" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137387607</v>
       </c>
       <c r="B18" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137387612</v>
       </c>
       <c r="B19" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137307711</v>
       </c>
       <c r="B20" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137311698</v>
       </c>
       <c r="B21" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137311764</v>
       </c>
       <c r="B22" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137387598</v>
       </c>
       <c r="B23" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137387602</v>
       </c>
       <c r="B24" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137387606</v>
       </c>
       <c r="B25" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137387610</v>
       </c>
       <c r="B26" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137307719</v>
       </c>
       <c r="B27" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137307720</v>
       </c>
       <c r="B28" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>137311693</v>
       </c>
       <c r="B29" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>137387597</v>
       </c>
       <c r="B30" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137387611</v>
       </c>
       <c r="B31" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>137307718</v>
       </c>
       <c r="B32" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>137307717</v>
       </c>
       <c r="B33" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>137311767</v>
       </c>
       <c r="B34" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>137387600</v>
       </c>
       <c r="B35" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>137387604</v>
       </c>
       <c r="B36" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>137311742</v>
       </c>
       <c r="B37" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>137311761</v>
       </c>
       <c r="B38" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>137311765</v>
       </c>
       <c r="B39" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>137311769</v>
       </c>
       <c r="B40" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>137307712</v>
       </c>
       <c r="B41" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>137307715</v>
       </c>
       <c r="B42" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>137311763</v>
       </c>
       <c r="B43" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>137311771</v>
       </c>
       <c r="B44" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>137387593</v>
       </c>
       <c r="B45" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>137387595</v>
       </c>
       <c r="B46" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>137311766</v>
       </c>
       <c r="B47" t="n">
-        <v>87555</v>
+        <v>87566</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>137307707</v>
       </c>
       <c r="B48" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>137307710</v>
       </c>
       <c r="B49" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>137307713</v>
       </c>
       <c r="B50" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>137307716</v>
       </c>
       <c r="B51" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>137311690</v>
       </c>
       <c r="B52" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>137311692</v>
       </c>
       <c r="B53" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         <v>137311697</v>
       </c>
       <c r="B54" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>137311708</v>
       </c>
       <c r="B55" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>137311760</v>
       </c>
       <c r="B56" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>137311773</v>
       </c>
       <c r="B57" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>137387601</v>
       </c>
       <c r="B58" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>137387609</v>
       </c>
       <c r="B59" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 20307-2025 artfynd.xlsx
+++ b/artfynd/A 20307-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137311694</v>
       </c>
       <c r="B2" t="n">
-        <v>91957</v>
+        <v>91958</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137307708</v>
       </c>
       <c r="B3" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137307721</v>
       </c>
       <c r="B4" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137311689</v>
       </c>
       <c r="B5" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137311695</v>
       </c>
       <c r="B6" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137311699</v>
       </c>
       <c r="B7" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137311700</v>
       </c>
       <c r="B8" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137311705</v>
       </c>
       <c r="B9" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137311707</v>
       </c>
       <c r="B10" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137311759</v>
       </c>
       <c r="B11" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137311772</v>
       </c>
       <c r="B12" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137311774</v>
       </c>
       <c r="B13" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137311777</v>
       </c>
       <c r="B14" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137387594</v>
       </c>
       <c r="B15" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137387603</v>
       </c>
       <c r="B16" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137387605</v>
       </c>
       <c r="B17" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137387607</v>
       </c>
       <c r="B18" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137387612</v>
       </c>
       <c r="B19" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137307711</v>
       </c>
       <c r="B20" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137311698</v>
       </c>
       <c r="B21" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137311764</v>
       </c>
       <c r="B22" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137387598</v>
       </c>
       <c r="B23" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137387602</v>
       </c>
       <c r="B24" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137387606</v>
       </c>
       <c r="B25" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137387610</v>
       </c>
       <c r="B26" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137307719</v>
       </c>
       <c r="B27" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137307720</v>
       </c>
       <c r="B28" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>137311693</v>
       </c>
       <c r="B29" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>137387597</v>
       </c>
       <c r="B30" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137387611</v>
       </c>
       <c r="B31" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>137307718</v>
       </c>
       <c r="B32" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>137307717</v>
       </c>
       <c r="B33" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>137311767</v>
       </c>
       <c r="B34" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>137387600</v>
       </c>
       <c r="B35" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>137387604</v>
       </c>
       <c r="B36" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>137311742</v>
       </c>
       <c r="B37" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>137311761</v>
       </c>
       <c r="B38" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>137311765</v>
       </c>
       <c r="B39" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>137311769</v>
       </c>
       <c r="B40" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>137307712</v>
       </c>
       <c r="B41" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>137307715</v>
       </c>
       <c r="B42" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>137311763</v>
       </c>
       <c r="B43" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>137311771</v>
       </c>
       <c r="B44" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>137387593</v>
       </c>
       <c r="B45" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>137387595</v>
       </c>
       <c r="B46" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>137311766</v>
       </c>
       <c r="B47" t="n">
-        <v>87566</v>
+        <v>87567</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>137307707</v>
       </c>
       <c r="B48" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>137307710</v>
       </c>
       <c r="B49" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>137307713</v>
       </c>
       <c r="B50" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>137307716</v>
       </c>
       <c r="B51" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>137311690</v>
       </c>
       <c r="B52" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>137311692</v>
       </c>
       <c r="B53" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         <v>137311697</v>
       </c>
       <c r="B54" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>137311708</v>
       </c>
       <c r="B55" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>137311760</v>
       </c>
       <c r="B56" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>137311773</v>
       </c>
       <c r="B57" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>137387601</v>
       </c>
       <c r="B58" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>137387609</v>
       </c>
       <c r="B59" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 20307-2025 artfynd.xlsx
+++ b/artfynd/A 20307-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137311694</v>
       </c>
       <c r="B2" t="n">
-        <v>91958</v>
+        <v>91961</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137307708</v>
       </c>
       <c r="B3" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137307721</v>
       </c>
       <c r="B4" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137311689</v>
       </c>
       <c r="B5" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137311695</v>
       </c>
       <c r="B6" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137311699</v>
       </c>
       <c r="B7" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137311700</v>
       </c>
       <c r="B8" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137311705</v>
       </c>
       <c r="B9" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137311707</v>
       </c>
       <c r="B10" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137311759</v>
       </c>
       <c r="B11" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137311772</v>
       </c>
       <c r="B12" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137311774</v>
       </c>
       <c r="B13" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137311777</v>
       </c>
       <c r="B14" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137387594</v>
       </c>
       <c r="B15" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137387603</v>
       </c>
       <c r="B16" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137387605</v>
       </c>
       <c r="B17" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137387607</v>
       </c>
       <c r="B18" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137387612</v>
       </c>
       <c r="B19" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137307711</v>
       </c>
       <c r="B20" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137311698</v>
       </c>
       <c r="B21" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137311764</v>
       </c>
       <c r="B22" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137387598</v>
       </c>
       <c r="B23" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137387602</v>
       </c>
       <c r="B24" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137387606</v>
       </c>
       <c r="B25" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137387610</v>
       </c>
       <c r="B26" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137307719</v>
       </c>
       <c r="B27" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137307720</v>
       </c>
       <c r="B28" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>137311693</v>
       </c>
       <c r="B29" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>137387597</v>
       </c>
       <c r="B30" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137387611</v>
       </c>
       <c r="B31" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>137307718</v>
       </c>
       <c r="B32" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>137307717</v>
       </c>
       <c r="B33" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>137311767</v>
       </c>
       <c r="B34" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>137387600</v>
       </c>
       <c r="B35" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>137387604</v>
       </c>
       <c r="B36" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>137311742</v>
       </c>
       <c r="B37" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>137311761</v>
       </c>
       <c r="B38" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>137311765</v>
       </c>
       <c r="B39" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>137311769</v>
       </c>
       <c r="B40" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>137307712</v>
       </c>
       <c r="B41" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>137307715</v>
       </c>
       <c r="B42" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>137311763</v>
       </c>
       <c r="B43" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>137311771</v>
       </c>
       <c r="B44" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>137387593</v>
       </c>
       <c r="B45" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>137387595</v>
       </c>
       <c r="B46" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>137311766</v>
       </c>
       <c r="B47" t="n">
-        <v>87567</v>
+        <v>87570</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>137307707</v>
       </c>
       <c r="B48" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>137307710</v>
       </c>
       <c r="B49" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>137307713</v>
       </c>
       <c r="B50" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>137307716</v>
       </c>
       <c r="B51" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>137311690</v>
       </c>
       <c r="B52" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>137311692</v>
       </c>
       <c r="B53" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         <v>137311697</v>
       </c>
       <c r="B54" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>137311708</v>
       </c>
       <c r="B55" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>137311760</v>
       </c>
       <c r="B56" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>137311773</v>
       </c>
       <c r="B57" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>137387601</v>
       </c>
       <c r="B58" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>137387609</v>
       </c>
       <c r="B59" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 20307-2025 artfynd.xlsx
+++ b/artfynd/A 20307-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137311694</v>
       </c>
       <c r="B2" t="n">
-        <v>91961</v>
+        <v>91965</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137307708</v>
       </c>
       <c r="B3" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137307721</v>
       </c>
       <c r="B4" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137311689</v>
       </c>
       <c r="B5" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137311695</v>
       </c>
       <c r="B6" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137311699</v>
       </c>
       <c r="B7" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137311700</v>
       </c>
       <c r="B8" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137311705</v>
       </c>
       <c r="B9" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137311707</v>
       </c>
       <c r="B10" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137311759</v>
       </c>
       <c r="B11" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137311772</v>
       </c>
       <c r="B12" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137311774</v>
       </c>
       <c r="B13" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137311777</v>
       </c>
       <c r="B14" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137387594</v>
       </c>
       <c r="B15" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137387603</v>
       </c>
       <c r="B16" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137387605</v>
       </c>
       <c r="B17" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137387607</v>
       </c>
       <c r="B18" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137387612</v>
       </c>
       <c r="B19" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137307711</v>
       </c>
       <c r="B20" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137311698</v>
       </c>
       <c r="B21" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137311764</v>
       </c>
       <c r="B22" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137387598</v>
       </c>
       <c r="B23" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137387602</v>
       </c>
       <c r="B24" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137387606</v>
       </c>
       <c r="B25" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137387610</v>
       </c>
       <c r="B26" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137307719</v>
       </c>
       <c r="B27" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137307720</v>
       </c>
       <c r="B28" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>137311693</v>
       </c>
       <c r="B29" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>137387597</v>
       </c>
       <c r="B30" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137387611</v>
       </c>
       <c r="B31" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>137307718</v>
       </c>
       <c r="B32" t="n">
-        <v>93497</v>
+        <v>93501</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>137307717</v>
       </c>
       <c r="B33" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>137311767</v>
       </c>
       <c r="B34" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>137387600</v>
       </c>
       <c r="B35" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>137387604</v>
       </c>
       <c r="B36" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>137311742</v>
       </c>
       <c r="B37" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>137311761</v>
       </c>
       <c r="B38" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>137311765</v>
       </c>
       <c r="B39" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>137311769</v>
       </c>
       <c r="B40" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>137307712</v>
       </c>
       <c r="B41" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>137307715</v>
       </c>
       <c r="B42" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>137311763</v>
       </c>
       <c r="B43" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>137311771</v>
       </c>
       <c r="B44" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>137387593</v>
       </c>
       <c r="B45" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>137387595</v>
       </c>
       <c r="B46" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>137311766</v>
       </c>
       <c r="B47" t="n">
-        <v>87570</v>
+        <v>87574</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>137307707</v>
       </c>
       <c r="B48" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>137307710</v>
       </c>
       <c r="B49" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>137307713</v>
       </c>
       <c r="B50" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>137307716</v>
       </c>
       <c r="B51" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>137311690</v>
       </c>
       <c r="B52" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>137311692</v>
       </c>
       <c r="B53" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         <v>137311697</v>
       </c>
       <c r="B54" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>137311708</v>
       </c>
       <c r="B55" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>137311760</v>
       </c>
       <c r="B56" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>137311773</v>
       </c>
       <c r="B57" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>137387601</v>
       </c>
       <c r="B58" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>137387609</v>
       </c>
       <c r="B59" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
